--- a/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_clap_xlnet-base-cased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_clap_xlnet-base-cased_zeroshot.xlsx
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.662299743999938</v>
+        <v>54.06099110599826</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002554099914666646</v>
+        <v>0.01802033036866608</v>
       </c>
     </row>
   </sheetData>
